--- a/public/frontend/exportsamples/importchoir.xlsx
+++ b/public/frontend/exportsamples/importchoir.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Laravel Projects\GSF\public\frontend\exportsamples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/MAMP/htdocs/gsf/public/frontend/exportsamples/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F087E630-924B-0E49-9201-2783180DE9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13185" windowHeight="4755"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="15460" windowHeight="10480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -36,9 +50,6 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>Sex</t>
-  </si>
-  <si>
     <t>sdsd@fff.com</t>
   </si>
   <si>
@@ -64,13 +75,16 @@
   </si>
   <si>
     <t>Choir</t>
+  </si>
+  <si>
+    <t>Gender</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -81,6 +95,13 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,9 +125,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -126,9 +148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -166,9 +188,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -203,7 +225,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -238,7 +260,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -411,16 +433,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -430,22 +452,22 @@
       <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>2367232</v>
@@ -454,18 +476,18 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>23267632</v>
@@ -474,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4">
         <v>9999</v>
@@ -491,18 +513,18 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
